--- a/docs/lab2/DHOPM_Lab2_SoSanh_KetQua.xlsx
+++ b/docs/lab2/DHOPM_Lab2_SoSanh_KetQua.xlsx
@@ -539,7 +539,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sinh viên: Nguyễn Thành Tâm | MSSV: 2312741 | Môn: Lập Trình Java Nâng Cao - ĐH Đà Lạt</t>
+          <t>Sinh viên: Nguyễn Thanh Tâm | MSSV: 2312741 | Môn: Lập Trình Java Nâng Cao - ĐH Đà Lạt</t>
         </is>
       </c>
     </row>
